--- a/nr-prepare-release-3.0.0-ballot/ig/StructureDefinition-fr-core-healthcare-service.xlsx
+++ b/nr-prepare-release-3.0.0-ballot/ig/StructureDefinition-fr-core-healthcare-service.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T15:58:11+00:00</t>
+    <t>2026-10-08T18:40:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-prepare-release-3.0.0-ballot/ig/StructureDefinition-fr-core-healthcare-service.xlsx
+++ b/nr-prepare-release-3.0.0-ballot/ig/StructureDefinition-fr-core-healthcare-service.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T18:40:11+00:00</t>
+    <t>2026-10-08T19:08:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-prepare-release-3.0.0-ballot/ig/StructureDefinition-fr-core-healthcare-service.xlsx
+++ b/nr-prepare-release-3.0.0-ballot/ig/StructureDefinition-fr-core-healthcare-service.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T19:08:49+00:00</t>
+    <t>2026-10-12T08:12:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
